--- a/pagina/data/informe_extranjeras.xlsx
+++ b/pagina/data/informe_extranjeras.xlsx
@@ -14,10 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico_mensual" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Categorias'!$A$1:$E$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Categorias'!$A$1:$E$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regiones'!$A$1:$C$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sexo_edad'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Historico_mensual'!$A$1:$D$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Historico_mensual'!$A$1:$D$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,6 +38,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
@@ -48,9 +51,6 @@
     <font>
       <i val="1"/>
       <color rgb="00595959"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <i val="1"/>
@@ -71,13 +71,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -99,22 +105,22 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -497,7 +503,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Centro Emergencia Mujer y Familia · Enero - Julio 2026 (preliminar)</t>
+          <t>Centro Emergencia Mujer y Familia · Enero - Agosto 2026 (preliminar)</t>
         </is>
       </c>
     </row>
@@ -508,7 +514,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1798</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +534,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>209</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7">
@@ -538,7 +544,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1589</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="9">
@@ -549,7 +555,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 10:33</t>
+          <t>2026-09-18 09:54</t>
         </is>
       </c>
     </row>
@@ -568,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -622,10 +628,10 @@
         </is>
       </c>
       <c r="D2" s="9" t="n">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>78</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -645,10 +651,10 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>20.1</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +677,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="5">
@@ -691,10 +697,10 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="6">
@@ -714,10 +720,10 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -737,10 +743,10 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -763,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9">
@@ -783,10 +789,10 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>42.1</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="10">
@@ -806,10 +812,10 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>30.6</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="11">
@@ -829,10 +835,10 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>27.3</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="12">
@@ -852,10 +858,10 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>74.2</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -875,10 +881,10 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>16.3</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="14">
@@ -898,10 +904,10 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="15">
@@ -921,10 +927,10 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>69.90000000000001</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -947,7 +953,7 @@
         <v>18</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="17">
@@ -967,10 +973,10 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="18">
@@ -990,10 +996,10 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="19">
@@ -1016,7 +1022,7 @@
         <v>7</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="20">
@@ -1036,10 +1042,10 @@
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="21">
@@ -1062,7 +1068,7 @@
         <v>4</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="22">
@@ -1085,7 +1091,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="23">
@@ -1108,7 +1114,7 @@
         <v>3</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="24">
@@ -1131,7 +1137,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="25">
@@ -1154,7 +1160,7 @@
         <v>2</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="26">
@@ -1177,7 +1183,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="27">
@@ -1200,7 +1206,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="28">
@@ -1211,19 +1217,19 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>tipo_violencia</t>
+          <t>pais_origen</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Psicológica</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>49.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="29">
@@ -1239,14 +1245,14 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Física</t>
+          <t>Psicológica</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>38.8</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="30">
@@ -1262,14 +1268,14 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Sexual</t>
+          <t>Física</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>11</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="31">
@@ -1285,37 +1291,37 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Económica o patrimonial</t>
+          <t>Sexual</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>0.5</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>mujeres</t>
+          <t>hombres</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>edad</t>
+          <t>tipo_violencia</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>18 a 59 años</t>
+          <t>Económica o patrimonial</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>1178</v>
+        <v>1</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>74.09999999999999</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="33">
@@ -1331,14 +1337,14 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>0 a 17 años</t>
+          <t>18 a 59 años</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>403</v>
+        <v>1321</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>25.4</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1354,14 +1360,14 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>60 a más años</t>
+          <t>0 a 17 años</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>8</v>
+        <v>470</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>0.5</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="35">
@@ -1372,19 +1378,19 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>discapacidad</t>
+          <t>edad</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>60 a más años</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>1560</v>
+        <v>8</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>98.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="36">
@@ -1400,14 +1406,14 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>29</v>
+        <v>1766</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>1.8</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="37">
@@ -1418,19 +1424,19 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>gestando</t>
+          <t>discapacidad</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>1526</v>
+        <v>33</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>96</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="38">
@@ -1446,14 +1452,14 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>63</v>
+        <v>1725</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>4</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -1464,19 +1470,19 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>lgtbi</t>
+          <t>gestando</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>1582</v>
+        <v>74</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>99.59999999999999</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="40">
@@ -1492,14 +1498,14 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>7</v>
+        <v>1792</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>0.4</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -1510,19 +1516,19 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>nivel_riesgo</t>
+          <t>lgtbi</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>733</v>
+        <v>7</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>46.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="42">
@@ -1538,14 +1544,14 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Severo</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>692</v>
+        <v>837</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>43.5</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="43">
@@ -1561,14 +1567,14 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Leve</t>
+          <t>Severo</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>164</v>
+        <v>784</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>10.3</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="44">
@@ -1579,19 +1585,19 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>vinculo_agresor</t>
+          <t>nivel_riesgo</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Vínculo relacional de pareja</t>
+          <t>Leve</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>1026</v>
+        <v>178</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>64.59999999999999</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="45">
@@ -1607,14 +1613,14 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Vínculo relacional familiar</t>
+          <t>Vínculo relacional de pareja</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>326</v>
+        <v>1157</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>20.5</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="46">
@@ -1630,14 +1636,14 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Sin vínculo relacional de pareja ni familiar</t>
+          <t>Vínculo relacional familiar</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>237</v>
+        <v>365</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>14.9</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="47">
@@ -1648,19 +1654,19 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>pais_origen</t>
+          <t>vinculo_agresor</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Sin vínculo relacional de pareja ni familiar</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1265</v>
+        <v>277</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>79.59999999999999</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="48">
@@ -1676,14 +1682,14 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>94</v>
+        <v>1418</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>5.9</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="49">
@@ -1699,14 +1705,14 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="50">
@@ -1722,14 +1728,14 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="51">
@@ -1745,14 +1751,14 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="52">
@@ -1768,14 +1774,14 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="53">
@@ -1791,14 +1797,14 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="54">
@@ -1814,14 +1820,14 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="55">
@@ -1837,14 +1843,14 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="56">
@@ -1860,11 +1866,11 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>0.4</v>
@@ -1883,11 +1889,11 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E57" s="10" t="n">
         <v>0.3</v>
@@ -1906,11 +1912,11 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>0.3</v>
@@ -1929,11 +1935,11 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>España</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E59" s="10" t="n">
         <v>0.3</v>
@@ -1952,11 +1958,11 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>0.2</v>
@@ -1975,14 +1981,14 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Suiza</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="62">
@@ -1998,7 +2004,7 @@
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Republica dominicana</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
@@ -2021,7 +2027,7 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
@@ -2044,11 +2050,11 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Republica dominicana</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" s="10" t="n">
         <v>0.1</v>
@@ -2067,7 +2073,7 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Belgica</t>
+          <t>Eslovaquia</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
@@ -2090,7 +2096,7 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Lituania</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
@@ -2113,7 +2119,7 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>Polonia</t>
+          <t>Tailandia</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
@@ -2136,7 +2142,7 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Ucrania</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
@@ -2159,7 +2165,7 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Rusia</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
@@ -2182,7 +2188,7 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Rusia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
@@ -2205,7 +2211,7 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>Lituania</t>
+          <t>Ucrania</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
@@ -2228,7 +2234,7 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Tailandia</t>
+          <t>Polonia</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
@@ -2251,7 +2257,7 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>Afganistan</t>
+          <t>Belgica</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
@@ -2269,19 +2275,19 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>tipo_violencia</t>
+          <t>pais_origen</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Física</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>692</v>
+        <v>1</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>43.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="75">
@@ -2292,19 +2298,19 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>tipo_violencia</t>
+          <t>pais_origen</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>Psicológica</t>
+          <t>Afganistan</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>571</v>
+        <v>1</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>35.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="76">
@@ -2320,14 +2326,14 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Sexual</t>
+          <t>Física</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>325</v>
+        <v>781</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>20.5</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="77">
@@ -2343,18 +2349,64 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
+          <t>Psicológica</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>639</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>mujeres</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>tipo_violencia</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>Sexual</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>377</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>mujeres</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>tipo_violencia</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
           <t>Económica o patrimonial</t>
         </is>
       </c>
-      <c r="D77" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" s="10" t="n">
+      <c r="D79" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" s="10" t="n">
         <v>0.1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E77"/>
+  <autoFilter ref="A1:E79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2397,20 +2449,20 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>827</v>
+        <v>941</v>
       </c>
       <c r="C2" s="10" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="C3" s="10" t="n">
         <v>6.9</v>
@@ -2419,14 +2471,14 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5">
@@ -2436,10 +2488,10 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="6">
@@ -2449,10 +2501,10 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -2462,10 +2514,10 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="8">
@@ -2475,10 +2527,10 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9">
@@ -2488,7 +2540,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>4.1</v>
@@ -2501,10 +2553,10 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="11">
@@ -2514,7 +2566,7 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>1.9</v>
@@ -2527,7 +2579,7 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C12" s="10" t="n">
         <v>1.6</v>
@@ -2540,7 +2592,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>1.4</v>
@@ -2549,24 +2601,24 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C15" s="10" t="n">
         <v>1.2</v>
@@ -2579,10 +2631,10 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
@@ -2595,17 +2647,17 @@
         <v>14</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" s="10" t="n">
         <v>0.6</v>
@@ -2614,14 +2666,14 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="B19" s="9" t="n">
         <v>11</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
@@ -2631,7 +2683,7 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C20" s="10" t="n">
         <v>0.5</v>
@@ -2644,7 +2696,7 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C21" s="10" t="n">
         <v>0.4</v>
@@ -2657,7 +2709,7 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22" s="10" t="n">
         <v>0.3</v>
@@ -2673,7 +2725,7 @@
         <v>5</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24">
@@ -2692,27 +2744,27 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>APURIMAC</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="B25" s="9" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>APURIMAC</t>
         </is>
       </c>
       <c r="B26" s="9" t="n">
         <v>3</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -2771,16 +2823,16 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>403</v>
+        <v>470</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>1178</v>
+        <v>1321</v>
       </c>
       <c r="D2" s="8" t="n">
         <v>8</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>1589</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="3">
@@ -2790,16 +2842,16 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>209</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4">
@@ -2809,16 +2861,16 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>566</v>
+        <v>657</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>1220</v>
+        <v>1371</v>
       </c>
       <c r="D4" s="8" t="n">
         <v>12</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>1798</v>
+        <v>2040</v>
       </c>
     </row>
   </sheetData>
@@ -2833,7 +2885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3007,7 +3059,7 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -3017,17 +3069,17 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>18 a 59 años</t>
+          <t>0 a 17 años</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -3041,13 +3093,13 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -3061,13 +3113,13 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -3081,13 +3133,13 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -3101,13 +3153,13 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -3121,13 +3173,13 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -3141,13 +3193,13 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -3157,17 +3209,17 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>60 a más años</t>
+          <t>18 a 59 años</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -3177,17 +3229,17 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>60 a más años</t>
+          <t>18 a 59 años</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3201,13 +3253,13 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3221,13 +3273,13 @@
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3241,13 +3293,13 @@
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -3267,7 +3319,7 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3287,67 +3339,67 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>0 a 17 años</t>
+          <t>60 a más años</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>0 a 17 años</t>
+          <t>60 a más años</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>0 a 17 años</t>
+          <t>60 a más años</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -3361,13 +3413,13 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -3381,13 +3433,13 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -3401,13 +3453,13 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -3421,13 +3473,13 @@
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -3437,17 +3489,17 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>18 a 59 años</t>
+          <t>0 a 17 años</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>167</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -3457,17 +3509,17 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>18 a 59 años</t>
+          <t>0 a 17 años</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>147</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -3477,17 +3529,17 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>18 a 59 años</t>
+          <t>0 a 17 años</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>164</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -3497,17 +3549,17 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>18 a 59 años</t>
+          <t>0 a 17 años</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>165</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -3521,13 +3573,13 @@
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>184</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -3541,13 +3593,13 @@
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>161</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -3561,13 +3613,13 @@
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>190</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -3577,17 +3629,17 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>60 a más años</t>
+          <t>18 a 59 años</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -3597,17 +3649,17 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>60 a más años</t>
+          <t>18 a 59 años</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>1</v>
+        <v>184</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -3617,17 +3669,17 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>60 a más años</t>
+          <t>18 a 59 años</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>1</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -3637,17 +3689,17 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>60 a más años</t>
+          <t>18 a 59 años</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -3657,17 +3709,17 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>60 a más años</t>
+          <t>18 a 59 años</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>2</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -3681,31 +3733,151 @@
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>60 a más años</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>60 a más años</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>60 a más años</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>60 a más años</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>60 a más años</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>Mujer</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>60 a más años</t>
         </is>
       </c>
-      <c r="D43" s="9" t="n">
+      <c r="D48" s="9" t="n">
         <v>3</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>60 a más años</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D43"/>
+  <autoFilter ref="A1:D49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>